--- a/光伏配储项目/电价数据/2026/金鹤站.xlsx
+++ b/光伏配储项目/电价数据/2026/金鹤站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.55398</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.61841</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1.00276</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.1614</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.11694</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1.06562</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.9210199999999999</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.92638</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44043</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.6234299999999999</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.6761</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.60903</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.9050199999999999</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.89966</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.6023099999999999</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.91501</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.9095599999999999</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.88878</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.9031</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.63201</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.91113</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39493</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.63121</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.9100499999999999</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.9161900000000001</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.65347</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.9409500000000001</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>1.02703</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.32428</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.40371</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.8760599999999999</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.6881699999999999</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.6828500000000001</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.46346</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.7484500000000001</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.77146</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.40179</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.38727</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.03415</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>1.02147</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>1.11284</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.75646</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.71313</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.5057</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.40904</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.40574</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.41016</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.7892899999999999</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.9719500000000001</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.33446</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.52798</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.7751699999999999</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.4284</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.78328</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.94863</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.91359</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>1.06572</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.3385</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.17483</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.19755</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.74309</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.23737</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>1.18594</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>1.10252</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.24538</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.5442</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.18264</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.26951</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.49085</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.32678</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.25048</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.42853</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.37023</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.30183</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.81223</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47924</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.41059</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41269</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.4219</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.18286</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.04258</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.18034</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53623</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5226499999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50627</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51481</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.69898</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.60041</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.6733</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.5791000000000001</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.57136</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.64539</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.61017</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.61603</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.61599</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.61026</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.6055499999999999</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.6604500000000001</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.91259</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.24239</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.92471</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.67702</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.5706599999999999</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.6296900000000001</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.5412899999999999</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.57033</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.9514199999999999</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.16547</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.79069</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.12683</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.05145</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>1.00862</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.7196399999999999</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.5526599999999999</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.5739500000000001</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.69129</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.18199</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.25216</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.49977</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1.18104</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.65381</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1.08707</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.83489</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.26807</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.15649</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.29161</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.6244</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.64708</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.5737300000000001</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.6252000000000001</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.19122</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>1.18939</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.19742</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.19113</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.98866</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.18521</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.2002</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.19484</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.67315</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.1838</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.24325</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.54058</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.45227</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.18941</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.50763</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.26544</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.75113</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.76423</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.9146</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44059</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43462</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41355</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33341</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.66764</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.79952</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.78385</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.58497</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.6527999999999999</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.5696599999999999</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1.16503</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.74971</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.7413</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.70184</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.6491399999999999</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.77134</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.5995199999999999</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.74274</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.55829</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37973</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.65112</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.57855</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.6407</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.60551</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.59745</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.60672</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.61213</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.5472</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.7019500000000001</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.8362000000000001</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.11537</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.87866</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.75844</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.70989</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.6075</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30779</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.64203</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.42595</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.7392300000000001</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.17659</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.54584</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.6891</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.18287</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.65191</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.19264</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>1.18599</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.80271</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.9609</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.18667</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1.18727</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.9020199999999999</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.5618</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.41425</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.47617</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.6776599999999999</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.17968</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>1.04365</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.18597</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.42188</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.26444</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1.18589</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.2204</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.21249</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.28349</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.29926</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.66157</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.1988</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.19865</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>1.05838</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>1.09357</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.11443</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.1005</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.22576</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.18469</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.26926</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>1.01262</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.76388</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.72093</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.53534</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.41272</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34314</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1.15179</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.81543</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.8026799999999999</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.72238</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.7718700000000001</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.94309</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.62687</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.7263200000000001</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.63058</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.79383</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.7437</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.6818200000000001</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.61782</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.6142000000000001</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.46117</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.5396799999999999</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.47062</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.48165</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.62052</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.71716</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.60512</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.58035</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.54215</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.5169400000000001</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.68301</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.72204</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.93845</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.18504</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.32758</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.85319</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.56994</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.66984</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.90939</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.8828400000000001</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.1797</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.44438</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.77661</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.9741799999999999</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.23121</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.70157</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.11985</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.52734</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.48976</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.66386</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>1.01421</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.11766</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.25935</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.18727</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1.08497</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>1.00236</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>1.03146</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.99541</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.27883</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.46312</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.80602</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.36935</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.6951</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.21727</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.85878</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>1.09389</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1.17655</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>1.12927</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>1.17551</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.27377</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.33537</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.17542</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.288</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.19762</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.18956</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.18606</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>1.20552</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>1.21302</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>1.19864</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1.17589</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1.1844</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.7354400000000001</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.52815</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.73883</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.33397</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32184</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.74751</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.49729</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.40585</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36479</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.33224</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.48191</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.50857</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.52755</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.33837</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.40365</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.46108</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.34242</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.43039</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.45957</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.72372</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.8562799999999999</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.6211</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.70877</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.73405</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.8538300000000001</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.71231</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.55641</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.55545</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.5440900000000001</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.5984400000000001</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.47556</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.09544</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.30665</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.28833</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.27916</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.55371</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.48809</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.5189900000000001</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.46798</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.6433</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.50836</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.48844</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.48876</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.49238</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.6029500000000001</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.4049</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.5102599999999999</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.50979</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.40914</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.48931</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35421</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.40986</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38171</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.40519</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34414</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.208</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.9846200000000001</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1.00001</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.59577</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.71323</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.65628</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.61593</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.6554500000000001</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.36378</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.6385299999999999</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.6376000000000001</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.90355</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.64618</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.64637</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.63681</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.6374500000000001</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.34172</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.63783</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.27455</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.07431</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04283</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04375</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04177</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.04613</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.27413</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.08356</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.29471</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.13021</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04679</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04668</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>0.00333</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04646</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.0454</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04233</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.30593</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04636</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04579</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.30365</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.30729</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.26263</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.27929</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.28717</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.29049</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.35724</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.38802</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.42732</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.36379</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.36462</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.35777</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.44755</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.6835</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.65319</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.38869</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.39251</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.66555</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.65434</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.65386</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.39678</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.36477</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33448</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.64965</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.56486</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.31168</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.27529</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.30815</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.30588</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.30511</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.30821</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.28892</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.28496</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15938</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.29246</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27221</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.30807</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.31157</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.31485</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.30288</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.38735</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.7556</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.89088</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.68633</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.6603600000000001</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.6784600000000001</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.76049</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.9559299999999999</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.4030899999999999</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.48275</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.73997</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.74241</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.90327</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.66375</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.54318</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.48411</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.45377</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.09072</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29532</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.37771</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.30169</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.38103</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.73985</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.7417</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.64846</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.60981</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.48065</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.7354700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7900900000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.78777</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.6066900000000001</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.7494</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>1.02581</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.42146</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.8540800000000001</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.45034</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.32803</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.8029700000000001</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.39628</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>1.05722</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.4166</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.77912</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.45696</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.78215</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.8007799999999999</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78769</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78535</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87858</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87901</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50234</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41209</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41185</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46051</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21895</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6393799999999999</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54134</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.70172</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.6770499999999999</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.6662400000000001</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.67084</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.67471</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.59317</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.67561</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.6644099999999999</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.5545800000000001</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.56069</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.56587</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38631</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.65425</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.6392599999999999</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.63942</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.6374</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.63815</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.6582100000000001</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.63874</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.6514800000000001</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.5565399999999999</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.68796</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.56072</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.60012</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43736</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.56436</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66669</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.07866</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.64397</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5065500000000001</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.5739099999999999</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.59754</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.00634</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.34111</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.30932</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.27374</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.56041</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.80083</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.57513</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.65425</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.55535</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.97641</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.78312</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.73198</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.64773</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.5803400000000001</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>1.00889</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>1.03503</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.5591499999999999</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.65999</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.72782</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.65873</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.70385</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.79279</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.69031</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.70274</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.5994700000000001</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.58645</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.70214</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.7317100000000001</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.7006599999999999</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.72821</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.73746</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.77549</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.7325900000000001</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.78103</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.7376200000000001</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.7392300000000001</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.73885</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.72801</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.72213</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.7004400000000001</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.7219099999999999</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.68971</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.65552</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.69578</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.66176</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.6753400000000001</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.6625599999999999</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.6545299999999999</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.64888</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.55391</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.95611</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.65118</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.7579600000000001</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.74281</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.7986599999999999</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.64274</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.6512899999999999</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.58751</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.62288</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37475</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35218</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.36381</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.5607000000000001</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.6554500000000001</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.41004</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.52522</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.62518</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.74151</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.88901</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.13702</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.93791</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.55452</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.12093</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.85853</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.96588</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.87525</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.64851</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.8254</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>1.08561</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.6496499999999999</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.52954</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.4358</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.37976</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.3767</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.89275</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>1.0959</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.73381</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1.21839</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.7984</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.8289800000000001</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.83369</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.7524500000000001</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.40668</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.39036</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.3759</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.47691</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.39452</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.36425</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.44423</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.38263</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.3708</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39762</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.50016</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.42006</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.35061</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.41555</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59675</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.19883</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.51588</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70359</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79534</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64978</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5836399999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.79945</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.43777</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.7619199999999999</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.18109</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.92961</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.65216</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.76659</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.70962</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.56924</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.17222</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.62638</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.9174500000000001</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.5908300000000001</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.67396</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.42918</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.35302</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.32095</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>1.56542</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>1.10152</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.53303</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.6108300000000001</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.86721</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.51988</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.75871</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>1.0885</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>1.08697</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.93335</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.94479</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.18183</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>1.173</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.8784999999999999</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>1.17352</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.62193</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.98697</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>1.03141</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>1.1733</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.96717</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>1.00783</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.59894</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.94014</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.9972000000000001</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>1.10455</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.9015299999999999</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.88916</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>1.11345</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.59054</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.9759500000000001</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>1.01094</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.75254</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38615</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.33684</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.73426</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.60285</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.6047</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34354</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.33504</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.59209</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.51228</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.62673</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.75003</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.61188</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.57857</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.60684</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.58217</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.62813</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.83475</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.72034</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.7031499999999999</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.93933</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>1.14473</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.65812</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.66108</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.66283</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.5982999999999999</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.59953</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.653</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.7442000000000001</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.7154700000000001</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.6580499999999999</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.5405599999999999</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.53512</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.54501</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.5473300000000001</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.37199</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.68789</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.37914</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.40303</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36158</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40541</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.61045</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.59253</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45664</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43992</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4392799999999999</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.59348</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.59112</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.59173</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34934</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.58717</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.49234</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46869</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.5260499999999999</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.7139800000000001</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.6463099999999999</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.6500499999999999</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.64278</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.66603</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.58223</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.6147400000000001</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.50973</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.44298</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.5089900000000001</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.44298</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.6186200000000001</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.64746</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.64642</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.63067</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.57843</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.57126</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.54083</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29471</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29393</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.55687</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.29385</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.28193</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26676</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30021</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30649</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.47206</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30694</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.36504</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31401</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.38327</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.48635</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.70378</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.6047100000000001</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.62702</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.8478300000000001</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.26933</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.1645</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.85104</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.45056</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.39635</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.42863</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.7006599999999999</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.9389299999999999</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.16616</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.12001</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.01679</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.5414600000000001</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.43867</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.42946</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39702</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39202</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.44675</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.41365</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.42553</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41871</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.5648099999999999</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.54379</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.5408999999999999</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.54379</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.51071</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.6214700000000001</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.44686</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.5099900000000001</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.4445</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.3435299999999999</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.5116700000000001</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.56699</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.62388</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.58999</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.66284</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.92364</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1.26403</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.41446</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.20131</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.9973</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.98602</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.9875900000000001</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.56314</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.55023</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.9448</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.08463</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.78881</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.01165</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.77282</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.65338</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.64611</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.71342</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.7981200000000001</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.2961</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.78142</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.37002</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.50512</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.17282</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.99988</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.66657</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.62882</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.66245</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.67582</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.67089</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.64787</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.67236</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.2068</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.7053</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.78708</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.70259</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.71037</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.71852</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.63767</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.75282</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.02007</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.12961</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.69643</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.70487</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.69864</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.77826</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.72843</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.8176599999999999</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.66979</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.46425</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>1.15996</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.54857</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.66292</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.5389400000000001</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.57212</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.34413</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34458</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.5333300000000001</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.68301</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.26527</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.5591499999999999</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.6201</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.39202</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.57289</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.54574</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.64127</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.62073</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.61811</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.54953</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.5248400000000001</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34617</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39801</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40249</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.42633</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.75119</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.49529</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.51251</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.52091</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29786</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30122</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28469</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.40743</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.45295</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.92699</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.47993</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.18574</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.9010199999999999</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.76223</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.44978</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.39429</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.45664</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.50017</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.49916</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.45014</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3677</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39308</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4029700000000001</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34929</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.37941</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.40551</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.40551</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30045</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.52275</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.39247</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.36758</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32577</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.38561</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.44992</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.75078</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.42726</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.51693</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.6939</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.49756</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.40638</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.41958</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.42792</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.42251</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.56612</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38968</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.42608</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.45469</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.40135</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.66762</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.4514</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38358</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43036</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38516</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65181</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83161</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47208</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40272</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45941</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34479</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.6053500000000001</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.5704</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.56548</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.9539099999999999</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.5537799999999999</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.5011</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.47545</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.42624</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.44557</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.42466</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.37702</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.43898</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.51602</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.41852</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.54513</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.76047</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.7670399999999999</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.27808</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.4818</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.34272</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.39396</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.54506</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.50117</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.7212000000000001</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.76134</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.55345</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.5013299999999999</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.45075</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.01897</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.48417</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.44441</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.09266</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.12804</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.08148</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.36877</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.11133</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>1.12791</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.01779</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.19356</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.14183</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.13087</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.17515</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.84166</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.19083</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.8482000000000001</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.34049</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.9022899999999999</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.71773</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.75662</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.9477300000000001</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.4825</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.62451</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.61346</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.6528099999999999</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.53185</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36016</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.7585499999999999</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.39696</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.53415</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.42756</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.59949</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.7645700000000001</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.75646</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.6122799999999999</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.5945900000000001</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.70865</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.72442</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.72792</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.60809</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.7345</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.61521</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.71514</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.57008</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.51467</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.5205700000000001</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.5205299999999999</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.56987</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.45172</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.53508</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.46261</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.69521</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.58258</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.53526</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.77028</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.59235</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.07808</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.78896</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.75366</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.29202</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.35289</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.73303</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.65561</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.36063</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>1.00097</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.60344</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.49778</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.4985</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.5450199999999999</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.59617</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.74442</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.19165</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.7000599999999999</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.9284199999999999</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.67448</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.95014</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.89523</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.75648</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.72601</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.18162</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.18281</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.44043</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.25312</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.64587</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.23138</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.28935</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.09882</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.42144</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1.03825</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.80624</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.7602899999999999</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.43862</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.23509</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.66377</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.48441</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.5394600000000001</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.46305</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42656</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40084</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37684</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.44936</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.48585</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40519</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.52946</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.5336799999999999</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.7997000000000001</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.67801</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.65995</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.50565</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>1.07873</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.68185</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.66454</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.79989</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.06889</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.18375</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.4999</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.19615</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.54644</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.15682</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.5571499999999999</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.5711499999999999</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.42764</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.50026</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.23487</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.3735</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.42958</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.48101</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.46152</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.5045500000000001</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.5110899999999999</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.46042</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41266</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43255</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.5413</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.5189600000000001</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.6031</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38455</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4060299999999999</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40312</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39931</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36413</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.75926</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.13469</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.77301</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.64886</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.48301</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.42228</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.39648</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.41243</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.38296</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.41878</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.35222</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.41966</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.34506</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.43458</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.38281</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.4978</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04337</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.3669</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.45984</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.32255</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.30941</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.44913</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.29921</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.37635</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.41257</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.44588</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.58669</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.48147</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.44912</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.39979</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.46316</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.44996</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.46425</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.55069</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.39248</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.4485</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.42453</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39815</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.41231</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.46071</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.4199</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.46863</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.58557</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.55969</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.5644</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.5826399999999999</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.54406</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.41536</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.38298</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.38322</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.94767</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.44335</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.57999</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.4474</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.45689</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.52564</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.5193</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.51423</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.51391</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.33233</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.37158</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.38247</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.23414</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.30692</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.27074</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.38665</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.38617</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.3044</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.31414</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.13778</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.72301</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.19925</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.38362</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.2682</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.12464</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.39894</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.69536</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.56453</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.30423</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.30425</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.28404</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.30567</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.4968</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.38515</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.3729</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.39102</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.61681</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.36557</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.39182</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.35394</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.36669</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.38247</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.39946</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.3994</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.38232</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.41394</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.42984</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.42653</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.39703</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.39255</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.38249</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.39269</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.38207</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.42829</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.80622</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.3833</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.46722</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.3927</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.38865</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.38867</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.38535</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.40184</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.48826</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.09943</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.37823</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1.00497</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.93199</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.5244099999999999</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.75805</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.75736</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.51412</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.41705</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.42857</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.42616</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.40826</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.41524</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.38737</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.44388</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.55755</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.42644</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.38824</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.44386</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.59362</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.99083</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.42496</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.6599299999999999</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.80165</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.45431</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.40278</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.75767</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.41129</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.52697</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.37395</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.37731</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.23379</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.07812</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.9743999999999999</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.3046</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.62676</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.54902</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.38744</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.49542</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.5806</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.7567699999999999</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.54903</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.5463600000000001</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.39629</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.22793</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.76015</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.75786</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.5812200000000001</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.45106</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.49591</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>1.00283</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.7675</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.6245299999999999</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.75701</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1.19256</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.6058</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.74197</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.63367</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.25609</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.8908700000000001</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.87562</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.89649</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.9150700000000001</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.16767</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.64642</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.94902</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.68869</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.9745900000000001</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.64424</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.66278</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.75084</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.64471</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.25664</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.04082</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1.01439</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.02481</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.53574</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.35583</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.05472</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.41023</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.38129</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.75789</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.38974</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.34542</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.55867</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.80526</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.5516599999999999</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.75473</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.7565499999999999</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.56114</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.47011</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.45967</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.4077</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.42897</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.41975</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.3708</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.38529</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.3835</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.36848</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.36175</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.38326</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.42274</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.40544</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.42729</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.63436</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5938300000000001</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.56116</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.54089</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.45092</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.47861</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.49808</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.55924</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.81287</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.16848</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.12805</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.04095</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.13078</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.74076</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.73551</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.05179</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.07016</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.67804</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.55492</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.56137</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.5568500000000001</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.47897</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.28602</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.47681</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.34828</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.54862</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.55088</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.54472</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.66025</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.55068</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>1.04897</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.6597000000000001</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.54884</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.49891</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.49926</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.48206</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.49917</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.48175</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.49949</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.5770700000000001</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.55696</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.5606100000000001</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.4975</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.5133099999999999</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.40313</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.38423</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.42309</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.49993</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.56055</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.6601</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.16683</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>1.07011</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.66096</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.58239</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.15994</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.8684400000000001</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.66039</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.15475</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.82853</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.4954</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.51122</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.49865</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.43959</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.53452</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.39156</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.39913</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34446</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.8675</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.6642</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.6714600000000001</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.93655</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.6470900000000001</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.47352</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.40029</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.39846</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.41967</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.40654</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.39281</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.35383</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.37941</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.36465</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.36296</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36232</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38738</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.62847</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.58747</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.42134</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.6376499999999999</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.02134</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.20065</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.9304</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.97712</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.02519</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.96758</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.93457</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.96489</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.94816</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.93232</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.93474</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.43563</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.75805</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>1.1245</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.71269</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>1.12083</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>1.21253</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>1.19439</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.71713</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.9383400000000001</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.85875</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.9256799999999999</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.54656</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.68179</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.70432</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.75269</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.20568</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.08589</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.0255</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.4123</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.33748</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.02101</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.12001</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.92475</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.75952</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.7587200000000001</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.8194400000000001</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.70112</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42434</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.69057</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.56586</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40162</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45852</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.69102</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.73491</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.69443</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.3687</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.7555299999999999</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40117</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.40317</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.38788</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36666</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.70459</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.46388</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.7435</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.5225700000000001</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.5087699999999999</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.44206</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>1.01326</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.91072</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.02458</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.91886</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>1.03241</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>1.01524</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>1.01542</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.26698</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.0851</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1.19315</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.54211</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.37503</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.67522</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.35479</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.61356</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.72987</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.7157100000000001</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.02404</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.71315</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.76617</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.14383</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.32534</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.53442</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.30209</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.46582</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>1.07477</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.50324</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.48248</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.75687</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.52436</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.52617</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.8109</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.7635299999999999</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.80598</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.67201</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37511</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27097</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.45696</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38802</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36748</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.75793</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.43962</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.41704</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.37231</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.37595</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.37278</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.49925</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37708</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38202</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.80977</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.3112</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.00236</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.93248</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.9587100000000001</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.03528</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.16341</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.06706</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.8627100000000001</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.69267</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.23197</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.21182</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.21285</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.14932</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.8654700000000001</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.70197</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.09447</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.10571</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.10574</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.13347</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.10341</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.5198200000000001</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.19876</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.6507000000000001</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.58192</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.15263</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.74182</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.67328</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1.18295</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.86885</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1.0817</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>1.06308</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.09191</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.03765</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.06759</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>1.12616</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.04907</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.05967</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.18324</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.16191</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.26185</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.20222</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.28579</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.16819</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.1846</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.11847</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.09911</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>1.12513</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1.17479</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1.19231</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.17294</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>1.09825</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.68364</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.62197</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.57157</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.55301</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.44867</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.3791600000000001</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37557</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.53984</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.31147</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.30884</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.06615</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.48045</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.51951</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.48816</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39874</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.46011</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.45838</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.47298</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.48699</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.47464</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39305</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38504</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.48058</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.47622</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.4741</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.46982</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.47327</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.46605</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.45576</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.45374</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.44408</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.45261</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.37216</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.84814</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.46223</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.37375</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.5728</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.69396</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.70957</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.66103</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.95037</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.7618200000000001</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.95572</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.16756</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.31894</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.46111</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.4486</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.45746</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.56019</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1.2614</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.85072</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.7486</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.73526</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.7002</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1.50198</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.8439099999999999</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.8762000000000001</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.23303</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.7745299999999999</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.57952</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.5833200000000001</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.6372100000000001</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.71904</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.5964299999999999</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.74514</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.61994</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1.20935</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.18463</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.41531</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.18636</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1.18442</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>1.19079</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>1.11758</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>1.09203</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>1.20701</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>1.11929</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>1.20547</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1.06543</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>1.09573</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>1.20604</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.09889</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.54849</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.80912</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.8038500000000001</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.5639299999999999</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.38089</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1.22433</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.84885</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.84935</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.55899</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.5544600000000001</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.5628</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.5154</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.55383</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.5211</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.50115</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.45967</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.45991</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38103</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.43858</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.39904</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38037</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.41206</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.49503</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.49908</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.5475399999999999</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.52025</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.55725</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.17506</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.8826000000000001</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.49314</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>1.18952</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.50865</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.56974</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.84439</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.79539</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.59709</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.85225</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.50313</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.52191</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.54484</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.17659</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.70064</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.55486</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.17864</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.5487799999999999</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.54963</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.5804600000000001</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.7992100000000001</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.55447</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.79787</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.8486699999999999</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>1.17359</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.79825</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.68326</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>1.07193</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>1.17476</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>1.1781</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.18098</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1.17883</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.8228799999999999</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.73415</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.65061</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.6817000000000001</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.7325700000000001</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.8337599999999999</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.81708</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.6192000000000001</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.8120700000000001</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.76136</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1.14094</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.76019</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.60914</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.64489</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.6430800000000001</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.61912</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.61554</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.71335</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.6754</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.8222999999999999</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.70392</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.6080399999999999</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.5309299999999999</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.51242</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40856</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38405</v>
       </c>
     </row>
   </sheetData>
